--- a/강의예제/4장_완성한_보고서_공유_및_출력하기/4장_복습.xlsx
+++ b/강의예제/4장_완성한_보고서_공유_및_출력하기/4장_복습.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-01 파일 이름" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파일 이름" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-04 외부 참조" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-08 유효성 검사" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-12 인쇄 설정" sheetId="5" state="visible" r:id="rId5"/>
@@ -620,7 +620,7 @@
     <row r="1">
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>4-01  파일 이름 짓기</t>
+          <t>파일 이름 짓기  (4장 03절 · 파일 버전 관리)</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
     <row r="5" ht="46" customHeight="1">
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>4-01 파일 이름</t>
+          <t>파일 이름</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
